--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,592 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129987559</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506526</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6577458</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129989261</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92884</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6577515</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129987702</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6577564</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129990047</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92884</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506481</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6577468</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129987672</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ekers grusgrop, Eker, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506521</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6577551</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129987559</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>129989261</v>
       </c>
       <c r="B4" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129987702</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1175,54 +1175,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129990047</v>
+        <v>129987672</v>
       </c>
       <c r="B6" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Ekers grusgrop, Eker, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506481</v>
+        <v>506521</v>
       </c>
       <c r="R6" t="n">
-        <v>6577468</v>
+        <v>6577551</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,7 +1250,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1260,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,50 +1287,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129987672</v>
+        <v>129990047</v>
       </c>
       <c r="B7" t="n">
-        <v>57734</v>
+        <v>92887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ekers grusgrop, Eker, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506521</v>
+        <v>506481</v>
       </c>
       <c r="R7" t="n">
-        <v>6577551</v>
+        <v>6577468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -938,54 +938,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129989261</v>
+        <v>129987702</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506484</v>
+        <v>506524</v>
       </c>
       <c r="R4" t="n">
-        <v>6577515</v>
+        <v>6577564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,59 +1059,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129987702</v>
+        <v>129989261</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>92887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungsholmen, Kungsholmen, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506524</v>
+        <v>506484</v>
       </c>
       <c r="R5" t="n">
-        <v>6577564</v>
+        <v>6577515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129987559</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,59 +938,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129987702</v>
+        <v>129989261</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>92888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungsholmen, Kungsholmen, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506524</v>
+        <v>506484</v>
       </c>
       <c r="R4" t="n">
-        <v>6577564</v>
+        <v>6577515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,54 +1054,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129989261</v>
+        <v>129987702</v>
       </c>
       <c r="B5" t="n">
-        <v>92887</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506484</v>
+        <v>506524</v>
       </c>
       <c r="R5" t="n">
-        <v>6577515</v>
+        <v>6577564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,50 +1175,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129987672</v>
+        <v>129990047</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>92888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekers grusgrop, Eker, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506521</v>
+        <v>506481</v>
       </c>
       <c r="R6" t="n">
-        <v>6577551</v>
+        <v>6577468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,54 +1291,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129990047</v>
+        <v>129987672</v>
       </c>
       <c r="B7" t="n">
-        <v>92887</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Ekers grusgrop, Eker, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506481</v>
+        <v>506521</v>
       </c>
       <c r="R7" t="n">
-        <v>6577468</v>
+        <v>6577551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129987559</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>129989261</v>
       </c>
       <c r="B4" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>129987702</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129990047</v>
       </c>
       <c r="B6" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1175,50 +1175,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129987672</v>
+        <v>129990047</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>92921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekers grusgrop, Eker, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506521</v>
+        <v>506481</v>
       </c>
       <c r="R6" t="n">
-        <v>6577551</v>
+        <v>6577468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,54 +1291,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129990047</v>
+        <v>129987672</v>
       </c>
       <c r="B7" t="n">
-        <v>92921</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Ekers grusgrop, Eker, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506481</v>
+        <v>506521</v>
       </c>
       <c r="R7" t="n">
-        <v>6577468</v>
+        <v>6577551</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129987559</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,54 +938,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129989261</v>
+        <v>129987702</v>
       </c>
       <c r="B4" t="n">
-        <v>92921</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506484</v>
+        <v>506524</v>
       </c>
       <c r="R4" t="n">
-        <v>6577515</v>
+        <v>6577564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,59 +1059,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129987702</v>
+        <v>129989261</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>92923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungsholmen, Kungsholmen, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506524</v>
+        <v>506484</v>
       </c>
       <c r="R5" t="n">
-        <v>6577564</v>
+        <v>6577515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>129990047</v>
       </c>
       <c r="B6" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>129987559</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -938,59 +938,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129987702</v>
+        <v>129989261</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungsholmen, Kungsholmen, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506524</v>
+        <v>506484</v>
       </c>
       <c r="R4" t="n">
-        <v>6577564</v>
+        <v>6577515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,54 +1054,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129989261</v>
+        <v>129987702</v>
       </c>
       <c r="B5" t="n">
-        <v>92923</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506484</v>
+        <v>506524</v>
       </c>
       <c r="R5" t="n">
-        <v>6577515</v>
+        <v>6577564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>129990047</v>
       </c>
       <c r="B6" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>129987672</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1401,6 +1401,126 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131890086</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>506525</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6577458</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>T-Öre-0155</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>131890086</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>131890086</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>131890086</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>496848</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506477.6198074664</v>
+        <v>506478</v>
       </c>
       <c r="R2" t="n">
-        <v>6577444.511142473</v>
+        <v>6577445</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,19 +759,9 @@
           <t>2002-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -817,47 +802,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129987559</v>
+        <v>129989261</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -866,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506526</v>
+        <v>506484</v>
       </c>
       <c r="R3" t="n">
-        <v>6577458</v>
+        <v>6577515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -911,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,14 +918,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129989261</v>
+        <v>129990047</v>
       </c>
       <c r="B4" t="n">
-        <v>93010</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -968,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506484</v>
+        <v>506481</v>
       </c>
       <c r="R4" t="n">
-        <v>6577515</v>
+        <v>6577468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,59 +1034,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129987702</v>
+        <v>129987672</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kungsholmen, Kungsholmen, Nrk</t>
+          <t>Ekers grusgrop, Eker, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506524</v>
+        <v>506521</v>
       </c>
       <c r="R5" t="n">
-        <v>6577564</v>
+        <v>6577551</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1148,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,50 +1146,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129987672</v>
+        <v>129987559</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ekers grusgrop, Eker, Nrk</t>
+          <t>Bäcktorp, Bäcktorp, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506521</v>
+        <v>506526</v>
       </c>
       <c r="R6" t="n">
-        <v>6577551</v>
+        <v>6577458</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1240,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,54 +1267,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129990047</v>
+        <v>129987702</v>
       </c>
       <c r="B7" t="n">
-        <v>93010</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäcktorp, Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506481</v>
+        <v>506524</v>
       </c>
       <c r="R7" t="n">
-        <v>6577468</v>
+        <v>6577564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131890086</v>
+        <v>129987770</v>
       </c>
       <c r="B8" t="n">
-        <v>99106</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,12 +1418,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1448,14 +1433,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bäcktorp, Nrk</t>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506525</v>
+        <v>506529</v>
       </c>
       <c r="R8" t="n">
-        <v>6577458</v>
+        <v>6577571</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,19 +1465,24 @@
           <t>Örebro</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>T-Öre-0155</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,15 +1497,252 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129987803</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kungsholmen, Kungsholmen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506509</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6577579</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131890086</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6577458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>T-Öre-0155</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Lotta Sörman</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/496848</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129989261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129990047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987672</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987559</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1385,6 +1415,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987702</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1627,6 +1667,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129987803</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1747,8 +1792,24 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131890086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,6 +1670,131 @@
       <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129987803</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131890086</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bäcktorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506525</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6577458</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>T-Öre-0155</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131890086</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1808,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 58832-2025 artfynd.xlsx
+++ b/artfynd/A 58832-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>131890086</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
